--- a/tests/SafeOpenXml.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe5d248fa8584a9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fa83699280541b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4a6b583d4f3e4203"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb3acd5e778024533"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a2f9a275fe4c84"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab345636276841a3"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fa83699280541b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3459cad987004b95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb3acd5e778024533"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6d938bb7f59442bd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab345636276841a3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5208a0f6ee74ec5"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3459cad987004b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ba1840fa9da4c73"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6d938bb7f59442bd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91fde5dacb774e24"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5208a0f6ee74ec5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32aa78129fb74069"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ba1840fa9da4c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R22ed205f99eb4904"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91fde5dacb774e24"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R122dc11a64d34d36"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32aa78129fb74069"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ebf85a0924446bb"/>
 </x:worksheet>
 </file>